--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N115_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N115_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.41010033022447</v>
+        <v>5.916641303661476</v>
       </c>
       <c r="D2" t="n">
-        <v>37.41310934549315</v>
+        <v>6.079630268642638</v>
       </c>
       <c r="E2" t="n">
-        <v>11.79577760158528</v>
+        <v>1.916813860257608</v>
       </c>
       <c r="F2" t="n">
-        <v>11.09382558408308</v>
+        <v>1.802746657413501</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.11744249828276</v>
+        <v>2.294084405970948</v>
       </c>
       <c r="D3" t="n">
-        <v>14.08399974977149</v>
+        <v>2.288649959337867</v>
       </c>
       <c r="E3" t="n">
-        <v>11.79577760158528</v>
+        <v>1.916813860257608</v>
       </c>
       <c r="F3" t="n">
-        <v>11.09382558408308</v>
+        <v>1.802746657413501</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.46028891430202</v>
+        <v>5.924796948574079</v>
       </c>
       <c r="D4" t="n">
-        <v>37.1883851875547</v>
+        <v>6.043112592977639</v>
       </c>
       <c r="E4" t="n">
-        <v>11.79577760158528</v>
+        <v>1.916813860257608</v>
       </c>
       <c r="F4" t="n">
-        <v>11.09382558408308</v>
+        <v>1.802746657413501</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.39626086990035</v>
+        <v>3.801892391358806</v>
       </c>
       <c r="D5" t="n">
-        <v>24.423531075578</v>
+        <v>3.968823799781426</v>
       </c>
       <c r="E5" t="n">
-        <v>11.79577760158528</v>
+        <v>1.916813860257608</v>
       </c>
       <c r="F5" t="n">
-        <v>11.09382558408308</v>
+        <v>1.802746657413501</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.33019898192772</v>
+        <v>4.928657334563255</v>
       </c>
       <c r="D6" t="n">
-        <v>30.19810180611507</v>
+        <v>4.907191543493698</v>
       </c>
       <c r="E6" t="n">
-        <v>11.79577760158528</v>
+        <v>1.916813860257608</v>
       </c>
       <c r="F6" t="n">
-        <v>11.09382558408308</v>
+        <v>1.802746657413501</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.67111510511255</v>
+        <v>3.684056204580789</v>
       </c>
       <c r="D7" t="n">
-        <v>23.54234262656944</v>
+        <v>3.825630676817533</v>
       </c>
       <c r="E7" t="n">
-        <v>11.79577760158528</v>
+        <v>1.916813860257608</v>
       </c>
       <c r="F7" t="n">
-        <v>11.09382558408308</v>
+        <v>1.802746657413501</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>7.13046419339489</v>
+        <v>1.15870043142667</v>
       </c>
       <c r="D8" t="n">
-        <v>6.987817228697914</v>
+        <v>1.135520299663411</v>
       </c>
       <c r="E8" t="n">
-        <v>11.79577760158528</v>
+        <v>1.916813860257608</v>
       </c>
       <c r="F8" t="n">
-        <v>11.09382558408308</v>
+        <v>1.802746657413501</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.5766078400476</v>
+        <v>5.456198774007735</v>
       </c>
       <c r="D9" t="n">
-        <v>33.79568161281204</v>
+        <v>5.491798262081956</v>
       </c>
       <c r="E9" t="n">
-        <v>11.79577760158528</v>
+        <v>1.916813860257608</v>
       </c>
       <c r="F9" t="n">
-        <v>11.09382558408308</v>
+        <v>1.802746657413501</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>8.013637950003956</v>
+        <v>1.302216166875643</v>
       </c>
       <c r="D10" t="n">
-        <v>8.947866694709321</v>
+        <v>1.454028337890265</v>
       </c>
       <c r="E10" t="n">
-        <v>11.79577760158528</v>
+        <v>1.916813860257608</v>
       </c>
       <c r="F10" t="n">
-        <v>11.09382558408308</v>
+        <v>1.802746657413501</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>10.62462226955914</v>
+        <v>1.726501118803361</v>
       </c>
       <c r="D11" t="n">
-        <v>10.15470646386876</v>
+        <v>1.650139800378674</v>
       </c>
       <c r="E11" t="n">
-        <v>11.79577760158528</v>
+        <v>1.916813860257608</v>
       </c>
       <c r="F11" t="n">
-        <v>11.09382558408308</v>
+        <v>1.802746657413501</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>31.16961548925403</v>
+        <v>5.06506251700378</v>
       </c>
       <c r="D12" t="n">
-        <v>31.02568719650551</v>
+        <v>5.041674169432146</v>
       </c>
       <c r="E12" t="n">
-        <v>11.79577760158528</v>
+        <v>1.916813860257608</v>
       </c>
       <c r="F12" t="n">
-        <v>11.09382558408308</v>
+        <v>1.802746657413501</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.59032469192931</v>
+        <v>4.158427762438514</v>
       </c>
       <c r="D13" t="n">
-        <v>25.10529345933094</v>
+        <v>4.079610187141278</v>
       </c>
       <c r="E13" t="n">
-        <v>11.79577760158528</v>
+        <v>1.916813860257608</v>
       </c>
       <c r="F13" t="n">
-        <v>11.09382558408308</v>
+        <v>1.802746657413501</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>35.90658364751934</v>
+        <v>5.834819842721893</v>
       </c>
       <c r="D14" t="n">
-        <v>35.42095190088902</v>
+        <v>5.755904683894467</v>
       </c>
       <c r="E14" t="n">
-        <v>11.79577760158528</v>
+        <v>1.916813860257608</v>
       </c>
       <c r="F14" t="n">
-        <v>11.09382558408308</v>
+        <v>1.802746657413501</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>31.07293113849231</v>
+        <v>5.049351310005</v>
       </c>
       <c r="D15" t="n">
-        <v>9.846673421162672</v>
+        <v>1.600084430938934</v>
       </c>
       <c r="E15" t="n">
-        <v>11.79577760158528</v>
+        <v>1.916813860257608</v>
       </c>
       <c r="F15" t="n">
-        <v>11.09382558408308</v>
+        <v>1.802746657413501</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>37.1067116483668</v>
+        <v>6.029840642859606</v>
       </c>
       <c r="D16" t="n">
-        <v>18.8152562027977</v>
+        <v>3.057479132954627</v>
       </c>
       <c r="E16" t="n">
-        <v>11.79577760158528</v>
+        <v>1.916813860257608</v>
       </c>
       <c r="F16" t="n">
-        <v>11.09382558408308</v>
+        <v>1.802746657413501</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>44.01714627935227</v>
+        <v>7.152786270394744</v>
       </c>
       <c r="D17" t="n">
-        <v>35.36960652440461</v>
+        <v>5.747561060215749</v>
       </c>
       <c r="E17" t="n">
-        <v>11.79577760158528</v>
+        <v>1.916813860257608</v>
       </c>
       <c r="F17" t="n">
-        <v>11.09382558408308</v>
+        <v>1.802746657413501</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>47.53519332124169</v>
+        <v>7.724468914701776</v>
       </c>
       <c r="D18" t="n">
-        <v>15.50323913625462</v>
+        <v>2.519276359641376</v>
       </c>
       <c r="E18" t="n">
-        <v>11.79577760158528</v>
+        <v>1.916813860257608</v>
       </c>
       <c r="F18" t="n">
-        <v>11.09382558408308</v>
+        <v>1.802746657413501</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>15.87800715175274</v>
+        <v>2.58017616215982</v>
       </c>
       <c r="D19" t="n">
-        <v>5.077182070575939</v>
+        <v>0.82504208646859</v>
       </c>
       <c r="E19" t="n">
-        <v>11.79577760158528</v>
+        <v>1.916813860257608</v>
       </c>
       <c r="F19" t="n">
-        <v>11.09382558408308</v>
+        <v>1.802746657413501</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
